--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SLB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SLB.xlsx
@@ -13,8 +13,8 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,11 @@
           <t>team_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,36 +472,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>primary_scorer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Slater | L. Barrett (17.8 net)</t>
+          <t>J. Slater (16.5 ppg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>most_used_player</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Barrett (29.6 mpg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>best_3pt_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Broussard (57.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Slater | L. Barrett (15.5 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>D. Relvao | J. Slater | L. Barrett (18.3 net)</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G. Crandall | J. Slater | L. Barrett (21.7 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -508,28 +548,623 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="41" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>playing_position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games_started</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bpg</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tp_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ft_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>efg_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ts_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>plus_minus_pg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>on_off_net_diff_per40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>role_tag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L. Barrett</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>59.1%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>66.5%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Slater</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>52.0%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>58.0%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>60.7%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>G. Crandall</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>60.5%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>59.1%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>61.0%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>56</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28</v>
+      </c>
+      <c r="H6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>84.2%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>22.9%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-33.8</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D. Relvao</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:U7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -578,7 +1213,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -661,22 +1296,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>22.5</v>
+        <v>43.9</v>
       </c>
       <c r="H2" t="n">
-        <v>87</v>
+        <v>90.3</v>
       </c>
       <c r="I2" t="n">
-        <v>69.2</v>
+        <v>74.8</v>
       </c>
       <c r="J2" t="n">
-        <v>17.8</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="3">
@@ -697,26 +1332,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D. Relvao | J. Slater</t>
+          <t>J. Slater | L. Barrett</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>19.4</v>
+        <v>43.9</v>
       </c>
       <c r="H3" t="n">
-        <v>88.7</v>
+        <v>90.3</v>
       </c>
       <c r="I3" t="n">
-        <v>66</v>
+        <v>74.8</v>
       </c>
       <c r="J3" t="n">
-        <v>22.7</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="4">
@@ -737,26 +1372,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D. Relvao | J. Slater</t>
+          <t>J. Slater | L. Barrett</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>19.4</v>
+        <v>43.9</v>
       </c>
       <c r="H4" t="n">
-        <v>88.7</v>
+        <v>90.3</v>
       </c>
       <c r="I4" t="n">
-        <v>66</v>
+        <v>74.8</v>
       </c>
       <c r="J4" t="n">
-        <v>22.7</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="5">
@@ -777,26 +1412,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D. Relvao | J. Slater | L. Barrett</t>
+          <t>G. Crandall | J. Slater | L. Barrett</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>15.3</v>
+        <v>27.7</v>
       </c>
       <c r="H5" t="n">
-        <v>91.7</v>
+        <v>88.2</v>
       </c>
       <c r="I5" t="n">
-        <v>73.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="J5" t="n">
-        <v>18.3</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="6">
@@ -817,26 +1452,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>D. Relvao | J. Slater | L. Barrett</t>
+          <t>G. Crandall | J. Slater | L. Barrett</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>15.3</v>
+        <v>27.7</v>
       </c>
       <c r="H6" t="n">
-        <v>91.7</v>
+        <v>88.2</v>
       </c>
       <c r="I6" t="n">
-        <v>73.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="J6" t="n">
-        <v>18.3</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="7">
@@ -857,26 +1492,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A. Broussard | J. Slater | L. Muhammad</t>
+          <t>G. Crandall | J. Slater | L. Barrett</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>13.7</v>
+        <v>27.7</v>
       </c>
       <c r="H7" t="n">
-        <v>72.8</v>
+        <v>88.2</v>
       </c>
       <c r="I7" t="n">
-        <v>58.3</v>
+        <v>66.5</v>
       </c>
       <c r="J7" t="n">
-        <v>14.6</v>
+        <v>21.7</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SLB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SLB.xlsx
@@ -13,9 +13,9 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Slater (16.5 ppg)</t>
+          <t>J. Slater (16.7 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Barrett (29.6 mpg)</t>
+          <t>L. Barrett (28.6 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,36 +508,60 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Broussard (57.1%)</t>
+          <t>L. Barrett (37.5%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>base_lineup</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Slater | L. Barrett (15.5 net)</t>
+          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva (12.1 min)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva (19.9 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Slater | L. Barrett (20.8 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>G. Crandall | J. Slater | L. Barrett (21.7 net)</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>G. Crandall | J. Slater | L. Barrett (27.2 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -548,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -694,43 +718,43 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
         <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="G2" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -740,19 +764,19 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>9.300000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -773,65 +797,65 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>58.5</v>
+        <v>79.8</v>
       </c>
       <c r="G3" t="n">
-        <v>29.3</v>
+        <v>26.6</v>
       </c>
       <c r="H3" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>6.5</v>
+        <v>11.7</v>
       </c>
       <c r="T3" t="n">
-        <v>29.6</v>
+        <v>29</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -856,69 +880,69 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>56.9</v>
+        <v>77.7</v>
       </c>
       <c r="G4" t="n">
-        <v>28.4</v>
+        <v>25.9</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>10.3</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6</v>
+        <v>11.6</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>high-minutes, efficient, impact</t>
         </is>
       </c>
     </row>
@@ -930,78 +954,74 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L5" t="n">
         <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.5</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>6.7</v>
+        <v>-14.7</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>high-minutes, primary-scorer</t>
         </is>
       </c>
     </row>
@@ -1013,74 +1033,78 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
-        <v>56</v>
-      </c>
-      <c r="G6" t="n">
-        <v>28</v>
-      </c>
-      <c r="H6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>-5.5</v>
+        <v>5.3</v>
       </c>
       <c r="T6" t="n">
-        <v>-33.8</v>
+        <v>6.3</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer</t>
+          <t>high-minutes, shooter, impact</t>
         </is>
       </c>
     </row>
@@ -1092,79 +1116,162 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>A. Dziewa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>61.1%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>63.9%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>71.1%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>D. Relvao</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>42</v>
-      </c>
-      <c r="G7" t="n">
-        <v>21</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="L8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U7"/>
+  <autoFilter ref="A1:U8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1175,28 +1282,219 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lineup_players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>team_rank_minutes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>team_rank_net</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>team_rank_defense</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>Base lineup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L2" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Best lineup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L4" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1213,7 +1511,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1296,22 +1594,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>43.9</v>
+        <v>59.6</v>
       </c>
       <c r="H2" t="n">
-        <v>90.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>74.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>15.5</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="3">
@@ -1332,26 +1630,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>J. Slater | L. Barrett</t>
+          <t>G. Crandall | J. Slater</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>43.9</v>
+        <v>58.2</v>
       </c>
       <c r="H3" t="n">
-        <v>90.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>74.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>15.5</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="4">
@@ -1372,26 +1670,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>J. Slater | L. Barrett</t>
+          <t>G. Crandall | L. Barrett</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>43.9</v>
+        <v>49.8</v>
       </c>
       <c r="H4" t="n">
-        <v>90.3</v>
+        <v>84.3</v>
       </c>
       <c r="I4" t="n">
-        <v>74.8</v>
+        <v>68.2</v>
       </c>
       <c r="J4" t="n">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="5">
@@ -1416,22 +1714,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>27.7</v>
+        <v>39.7</v>
       </c>
       <c r="H5" t="n">
-        <v>88.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>66.5</v>
+        <v>60.4</v>
       </c>
       <c r="J5" t="n">
-        <v>21.7</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="6">
@@ -1452,26 +1750,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>G. Crandall | J. Slater | L. Barrett</t>
+          <t>A. Broussard | G. Crandall | J. Slater</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>27.7</v>
+        <v>33.1</v>
       </c>
       <c r="H6" t="n">
-        <v>88.2</v>
+        <v>108.6</v>
       </c>
       <c r="I6" t="n">
-        <v>66.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>21.7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -1496,22 +1794,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>27.7</v>
+        <v>39.7</v>
       </c>
       <c r="H7" t="n">
-        <v>88.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>66.5</v>
+        <v>60.4</v>
       </c>
       <c r="J7" t="n">
-        <v>21.7</v>
+        <v>27.2</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SLB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SLB.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Slater (16.7 ppg)</t>
+          <t>J. Slater (18.2 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Barrett (28.6 mpg)</t>
+          <t>L. Barrett (28.1 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Barrett (37.5%)</t>
+          <t>E. Francisco (40.0%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva (12.1 min)</t>
+          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva (18.7 min)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva (19.9 net)</t>
+          <t>A. Broussard | A. Dziewa | J. Slater | L. Barrett | L. Muhammad (39.6 net)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Slater | L. Barrett (20.8 net)</t>
+          <t>J. Slater | L. Barrett (19.3 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>G. Crandall | J. Slater | L. Barrett (27.2 net)</t>
+          <t>A. Broussard | A. Dziewa | L. Muhammad (18.6 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -718,43 +718,43 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>85.8</v>
+        <v>112.6</v>
       </c>
       <c r="G2" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
       <c r="H2" t="n">
-        <v>14.3</v>
+        <v>15.2</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -764,19 +764,19 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="T2" t="n">
-        <v>-10.1</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -797,43 +797,43 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>79.8</v>
+        <v>105.4</v>
       </c>
       <c r="G3" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="H3" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -843,19 +843,19 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>11.7</v>
+        <v>11</v>
       </c>
       <c r="T3" t="n">
-        <v>29</v>
+        <v>21.5</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -871,78 +871,74 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>G. Crandall</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+          <t>L. Muhammad</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>77.7</v>
+        <v>103.3</v>
       </c>
       <c r="G4" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>10.3</v>
+        <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>11.6</v>
+        <v>-7.6</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, efficient, impact</t>
+          <t>high-minutes, primary-scorer</t>
         </is>
       </c>
     </row>
@@ -954,74 +950,78 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Muhammad</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>A. Broussard</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>77.7</v>
+        <v>101.8</v>
       </c>
       <c r="G5" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="H5" t="n">
-        <v>12.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-14.7</v>
+        <v>17.8</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer</t>
+          <t>high-minutes, impact</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Broussard</t>
+          <t>G. Crandall</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1042,69 +1042,69 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>75.90000000000001</v>
+        <v>101.6</v>
       </c>
       <c r="G6" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="H6" t="n">
-        <v>10.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>5.3</v>
+        <v>8.5</v>
       </c>
       <c r="T6" t="n">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>high-minutes, shooter, impact</t>
+          <t>high-minutes</t>
         </is>
       </c>
     </row>
@@ -1125,65 +1125,65 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>58.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>19.4</v>
+        <v>20.2</v>
       </c>
       <c r="H7" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1</v>
+        <v>0.8</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1208,43 +1208,43 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>58.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>-1.8</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1270,8 +1270,91 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>E. Francisco</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>68.7%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>efficient, shooter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U8"/>
+  <autoFilter ref="A1:U9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1282,10 +1365,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1378,31 +1461,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>12.1</v>
+        <v>18.7</v>
       </c>
       <c r="G2" t="n">
-        <v>82.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>62.9</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>19.9</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -1418,35 +1501,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva</t>
+          <t>A. Broussard | A. Dziewa | J. Slater | L. Barrett | L. Muhammad</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>12.1</v>
       </c>
       <c r="G3" t="n">
-        <v>82.8</v>
+        <v>99</v>
       </c>
       <c r="H3" t="n">
-        <v>62.9</v>
+        <v>59.4</v>
       </c>
       <c r="I3" t="n">
-        <v>19.9</v>
+        <v>39.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -1462,39 +1545,83 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>D. Relvao | G. Crandall | J. Slater | L. Barrett | L. Silva</t>
+          <t>A. Broussard | A. Dziewa | J. Slater | L. Barrett | L. Muhammad</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>12.1</v>
       </c>
       <c r="G4" t="n">
-        <v>82.8</v>
+        <v>99</v>
       </c>
       <c r="H4" t="n">
-        <v>62.9</v>
+        <v>59.4</v>
       </c>
       <c r="I4" t="n">
-        <v>19.9</v>
+        <v>39.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L4" t="n">
-        <v>19</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SL Benfica</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A. Broussard | A. Dziewa | G. Crandall | J. Slater | L. Muhammad</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>22</v>
+      </c>
+      <c r="L5" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1594,22 +1721,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>59.6</v>
+        <v>76.8</v>
       </c>
       <c r="H2" t="n">
-        <v>89.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="I2" t="n">
-        <v>69.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="J2" t="n">
-        <v>20.8</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="3">
@@ -1630,26 +1757,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>G. Crandall | J. Slater</t>
+          <t>A. Broussard | J. Slater</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>58.2</v>
+        <v>64.2</v>
       </c>
       <c r="H3" t="n">
-        <v>93.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="I3" t="n">
-        <v>70.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="J3" t="n">
-        <v>23.4</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="4">
@@ -1670,26 +1797,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>G. Crandall | L. Barrett</t>
+          <t>A. Dziewa | J. Slater</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>49.8</v>
+        <v>42.2</v>
       </c>
       <c r="H4" t="n">
-        <v>84.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="J4" t="n">
-        <v>16.1</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="5">
@@ -1710,26 +1837,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>G. Crandall | J. Slater | L. Barrett</t>
+          <t>A. Broussard | A. Dziewa | L. Muhammad</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>39.7</v>
+        <v>51.7</v>
       </c>
       <c r="H5" t="n">
-        <v>87.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>60.4</v>
+        <v>66.5</v>
       </c>
       <c r="J5" t="n">
-        <v>27.2</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="6">
@@ -1750,26 +1877,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A. Broussard | G. Crandall | J. Slater</t>
+          <t>A. Broussard | J. Slater | L. Barrett</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>33.1</v>
+        <v>35.5</v>
       </c>
       <c r="H6" t="n">
-        <v>108.6</v>
+        <v>104.7</v>
       </c>
       <c r="I6" t="n">
-        <v>79.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="7">
@@ -1790,26 +1917,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>G. Crandall | J. Slater | L. Barrett</t>
+          <t>A. Broussard | A. Dziewa | L. Muhammad</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>39.7</v>
+        <v>51.7</v>
       </c>
       <c r="H7" t="n">
-        <v>87.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>60.4</v>
+        <v>66.5</v>
       </c>
       <c r="J7" t="n">
-        <v>27.2</v>
+        <v>18.6</v>
       </c>
     </row>
   </sheetData>
